--- a/backend/dataset.xlsx
+++ b/backend/dataset.xlsx
@@ -97,16 +97,16 @@
     <t>Break down your program, talk abt each element. Focus on taking it one at time, instead of focusing on full program. Use a mental checklist to check things off</t>
   </si>
   <si>
-    <t>Talk them through what to expect. Remind them that this is for fun and think about why you do this. It was your choice to compete, so enjoy it and have fun</t>
+    <t>Talk to your coach about what to expect. Think about why you do this. It was your choice to compete, so enjoy it and have fun!</t>
   </si>
   <si>
     <t>This is your journey and we are here every step. No matter how you skate, we'll be proud of you for going out there and trying your best. Remember why you skate, it's for yourself.</t>
   </si>
   <si>
-    <t>Remind them that it's your first year in level. With so many new things like levels and elements, whatever is, it's just a starting point. You will grow into this level, so don't expect highest score or highest placement.</t>
-  </si>
-  <si>
-    <t>That is out of ur control, so focus on what u can control and try to put out ur best skate and something you're proud of. Let everything else fall into place bc it's out of ur hands.</t>
+    <t>It is your first season at this level. With so many new things such as elements and levels, whatever it is, it is just a starting point. You will grow into this level, so don't expect highest score or highest placement at first few competitions.</t>
+  </si>
+  <si>
+    <t>That is out of your control, so focus on what you can control and try to put out your best skate and something you're proud of. Let everything else fall into place because it's out of your hands.</t>
   </si>
   <si>
     <t>Everyone's skating journey is different, and everyone is on a different timeline. Don't focus on others, focus on your own journey. Think about why u do this instead of comparing urself to someone else.</t>
@@ -115,13 +115,13 @@
     <t>You did great job recovering because it is a very tough thing to recover from a mistake, and you had the mental toughness to keep going. Don't focus on one mistake because there were lots of other good things from performance.</t>
   </si>
   <si>
-    <t>Let ur training speak for itself. If you have put in the training and listened to coach's guidance about run throughs and cardio training, it will help you get through program. Nothing changes from training to competition. Focus on other factors of the program like performance instead of just will I make it.</t>
-  </si>
-  <si>
-    <t>Ask them how it felt and why are you disappointed. Many other good things I saw in your performance. It's ok to have these feelings (validate them), since you cant always be perfectly happy about a skate, but in the end, you did the best as you could and it can only go up from here.</t>
-  </si>
-  <si>
-    <t>This is a good thing since you can get it out way right now. When you do in program, you'll be more aware at that area and it's a good reminder.</t>
+    <t>Let your training speak for itself. If you have put in the training and listened to coach's guidance about run throughs and cardio training, it will help you get through program. Nothing changes from training to competition. Focus on other factors of the program like performance instead of just will I make it.</t>
+  </si>
+  <si>
+    <t>Tell me why you are disappointed? There were many other good things I saw in your performance. It's valid to have these feelings, since you can't always be perfectly happy about a skate. But in the end, you did the best you could and it can only go up from here.</t>
+  </si>
+  <si>
+    <t>This is a good thing since you can get it out way right now. When you do it in program, you'll be more aware at that area and it's a good reminder.</t>
   </si>
   <si>
     <t>Don't worry about your order since order won't impact what you do. No matter when you skate, you put out what you trained to perform. Don't let it overwhelm what you have to do out on ice.</t>
